--- a/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_0.0001_80_10_rnd_e/test_res/model_rnd_e_matpes_lr0.0001_80_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_0.0001_80_10_rnd_e/test_res/model_rnd_e_matpes_lr0.0001_80_10_test.xlsx
@@ -27057,243 +27057,273 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_configs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rmse</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Fe12B3Si3</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>test_energy</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>48</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>71.36308570998041</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>70.94933677101314</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Fe12Si4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>test_energy</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5.172612922840254</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4.808194617661381</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Fe16</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>test_energy</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>11</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>6.651857794400679</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>6.094816134180126</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Fe34B10Si10</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Fe34B10Si10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>test_energy</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>133</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>9.337884964918784</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>8.338329131044121</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Fe8B4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>test_energy</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>130.1434283015621</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>130.1340352732624</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Fe12B3Si3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>train_energy</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>132</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>71.36652948000624</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>71.10026824160848</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Fe12Si4</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>train_energy</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>39</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>5.244371139333275</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>4.905662204604736</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Fe16</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>train_energy</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>40</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>8.987460320872609</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7.7748407944664</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Fe34B10Si10</t>
-        </is>
+      <c r="A10" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Fe34B10Si10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>train_energy</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>590</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>9.358865925813239</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>8.296824167707346</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Fe8B4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>train_energy</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>44</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>422.6254682350259</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>188.5055253943464</v>
       </c>
     </row>
